--- a/SGC-CKN/Excel/bf4550f8-36ad-4cf6-8eb1-176b10819b66_Lô_CT-02_P7-156_D800_25-03-2026.xlsx
+++ b/SGC-CKN/Excel/bf4550f8-36ad-4cf6-8eb1-176b10819b66_Lô_CT-02_P7-156_D800_25-03-2026.xlsx
@@ -119,7 +119,7 @@
 25/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">10:10
+    <t xml:space="preserve">10:20
 25/03/2026</t>
   </si>
   <si>
@@ -157,7 +157,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">13:20
+    <t xml:space="preserve">13:30
 25/03/2026</t>
   </si>
   <si>
@@ -403,12 +403,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -579,17 +579,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1290,50 +1290,50 @@
         <v>-9.89</v>
       </c>
       <c r="H12" s="9">
-        <v>0.48</v>
+        <v>0.65</v>
       </c>
       <c r="I12" s="9">
         <v>2.9</v>
       </c>
-      <c r="J12" s="8">
-        <v>6</v>
+      <c r="J12" s="12">
+        <v>4.46</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <v>-9.89</v>
       </c>
-      <c r="G13" s="12">
-        <v>-12.09</v>
-      </c>
-      <c r="H13" s="12">
+      <c r="G13" s="13">
+        <v>-17.09</v>
+      </c>
+      <c r="H13" s="13">
         <v>1.15</v>
       </c>
-      <c r="I13" s="12">
-        <v>2.2</v>
-      </c>
-      <c r="J13" s="15">
-        <v>1.91</v>
-      </c>
-      <c r="K13" s="13" t="s">
+      <c r="I13" s="13">
+        <v>7.2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>6.26</v>
+      </c>
+      <c r="K13" s="14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         <v>42</v>
       </c>
       <c r="F14" s="16">
-        <v>-12.09</v>
+        <v>-17.09</v>
       </c>
       <c r="G14" s="16">
         <v>-21.39</v>
@@ -1363,10 +1363,10 @@
         <v>0.48</v>
       </c>
       <c r="I14" s="16">
-        <v>9.3</v>
+        <v>4.3</v>
       </c>
       <c r="J14" s="8">
-        <v>19.24</v>
+        <v>8.9</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1395,13 +1395,13 @@
         <v>-25.79</v>
       </c>
       <c r="H15" s="19">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="I15" s="19">
         <v>4.4</v>
       </c>
-      <c r="J15" s="15">
-        <v>3.3</v>
+      <c r="J15" s="12">
+        <v>2.93</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1462,16 +1462,16 @@
         <v>-35.19</v>
       </c>
       <c r="G17" s="25">
-        <v>-40.78</v>
+        <v>-37.78</v>
       </c>
       <c r="H17" s="25">
         <v>1</v>
       </c>
       <c r="I17" s="25">
-        <v>5.59</v>
-      </c>
-      <c r="J17" s="8">
-        <v>5.59</v>
+        <v>2.59</v>
+      </c>
+      <c r="J17" s="12">
+        <v>2.59</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1494,19 +1494,19 @@
         <v>57</v>
       </c>
       <c r="F18" s="28">
-        <v>-40.78</v>
+        <v>-37.78</v>
       </c>
       <c r="G18" s="28">
-        <v>-44.2</v>
+        <v>-39.5</v>
       </c>
       <c r="H18" s="28">
         <v>0.87</v>
       </c>
       <c r="I18" s="28">
-        <v>3.42</v>
-      </c>
-      <c r="J18" s="15">
-        <v>3.95</v>
+        <v>1.72</v>
+      </c>
+      <c r="J18" s="12">
+        <v>1.98</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1529,7 +1529,7 @@
         <v>60</v>
       </c>
       <c r="F19" s="31">
-        <v>-44.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G19" s="31">
         <v>-44.2</v>
@@ -1538,10 +1538,10 @@
         <v>1.65</v>
       </c>
       <c r="I19" s="31">
-        <v>0</v>
-      </c>
-      <c r="J19" s="15">
-        <v>0</v>
+        <v>4.7</v>
+      </c>
+      <c r="J19" s="12">
+        <v>2.85</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>61</v>
@@ -1567,16 +1567,16 @@
         <v>-44.2</v>
       </c>
       <c r="G20" s="34">
-        <v>-45.1</v>
+        <v>-45.7</v>
       </c>
       <c r="H20" s="34">
         <v>2.62</v>
       </c>
       <c r="I20" s="34">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J20" s="37">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1766,42 +1766,42 @@
         <v>-9.89</v>
       </c>
       <c r="G3" s="9">
-        <v>0.48</v>
+        <v>0.65</v>
       </c>
       <c r="H3" s="9">
         <v>2.9</v>
       </c>
-      <c r="I3" s="8">
-        <v>6</v>
+      <c r="I3" s="12">
+        <v>4.46</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <v>-9.89</v>
       </c>
-      <c r="F4" s="12">
-        <v>-12.09</v>
-      </c>
-      <c r="G4" s="12">
+      <c r="F4" s="13">
+        <v>-17.09</v>
+      </c>
+      <c r="G4" s="13">
         <v>1.15</v>
       </c>
-      <c r="H4" s="12">
-        <v>2.2</v>
-      </c>
-      <c r="I4" s="15">
-        <v>1.91</v>
+      <c r="H4" s="13">
+        <v>7.2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>6.26</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-12.09</v>
+        <v>-17.09</v>
       </c>
       <c r="F5" s="16">
         <v>-21.39</v>
@@ -1827,10 +1827,10 @@
         <v>0.48</v>
       </c>
       <c r="H5" s="16">
-        <v>9.3</v>
+        <v>4.3</v>
       </c>
       <c r="I5" s="8">
-        <v>19.24</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1853,13 +1853,13 @@
         <v>-25.79</v>
       </c>
       <c r="G6" s="19">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="19">
         <v>4.4</v>
       </c>
-      <c r="I6" s="15">
-        <v>3.3</v>
+      <c r="I6" s="12">
+        <v>2.93</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1908,16 +1908,16 @@
         <v>-35.19</v>
       </c>
       <c r="F8" s="25">
-        <v>-40.78</v>
+        <v>-37.78</v>
       </c>
       <c r="G8" s="25">
         <v>1</v>
       </c>
       <c r="H8" s="25">
-        <v>5.59</v>
-      </c>
-      <c r="I8" s="8">
-        <v>5.59</v>
+        <v>2.59</v>
+      </c>
+      <c r="I8" s="12">
+        <v>2.59</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1934,19 +1934,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-40.78</v>
+        <v>-37.78</v>
       </c>
       <c r="F9" s="28">
-        <v>-44.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G9" s="28">
         <v>0.87</v>
       </c>
       <c r="H9" s="28">
-        <v>3.42</v>
-      </c>
-      <c r="I9" s="15">
-        <v>3.95</v>
+        <v>1.72</v>
+      </c>
+      <c r="I9" s="12">
+        <v>1.98</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1963,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-44.2</v>
+        <v>-39.5</v>
       </c>
       <c r="F10" s="31">
         <v>-44.2</v>
@@ -1972,10 +1972,10 @@
         <v>1.65</v>
       </c>
       <c r="H10" s="31">
-        <v>0</v>
-      </c>
-      <c r="I10" s="15">
-        <v>0</v>
+        <v>4.7</v>
+      </c>
+      <c r="I10" s="12">
+        <v>2.85</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1995,16 +1995,16 @@
         <v>-44.2</v>
       </c>
       <c r="F11" s="34">
-        <v>-45.1</v>
+        <v>-45.7</v>
       </c>
       <c r="G11" s="34">
         <v>2.62</v>
       </c>
       <c r="H11" s="34">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="I11" s="37">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2024,16 +2024,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="40">
-        <v>-45.1</v>
+        <v>-45.7</v>
       </c>
       <c r="G12" s="40">
-        <v>11.22</v>
+        <v>11.55</v>
       </c>
       <c r="H12" s="40">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="I12" s="40">
-        <v>4.02</v>
+        <v>3.96</v>
       </c>
     </row>
   </sheetData>
